--- a/模板_多产品成本归集表.xlsx
+++ b/模板_多产品成本归集表.xlsx
@@ -36,7 +36,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -45,14 +45,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00166534"/>
-        <bgColor rgb="00166534"/>
+        <fgColor rgb="001e3a5f"/>
+        <bgColor rgb="001e3a5f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F5F9"/>
         <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E8FF"/>
+        <bgColor rgb="00F3E8FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,12 +85,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -471,8 +480,8 @@
     <col width="12.4" customWidth="1" min="11" max="11"/>
     <col width="12.4" customWidth="1" min="12" max="12"/>
     <col width="16.3" customWidth="1" min="13" max="13"/>
-    <col width="9.800000000000001" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="11.1" customWidth="1" min="14" max="14"/>
+    <col width="9.800000000000001" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,10 +552,14 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>制造费用(¥)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -594,57 +607,61 @@
       <c r="M2" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="N2" s="2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>PRD-B001</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>产品B-轻量型</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>LITE-150W</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>27000</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>4875</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="4" t="n">
         <v>2400</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="N3" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -692,12 +709,14 @@
       <c r="M4" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>客户定制批次</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
